--- a/resultados/resultado_turma.xlsx
+++ b/resultados/resultado_turma.xlsx
@@ -7,7 +7,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Chaves do Cofre" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Água para Todos" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Revisar" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,194 +427,1534 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T2"/>
+  <dimension ref="A1:U6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>arquivo</t>
+          <t>Código</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>nome_estudante</t>
+          <t>Nome</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>ano</t>
+          <t>Nome - Status</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>q1_alternativa</t>
+          <t>Ano</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>q1_status</t>
+          <t>Q1 - Alternativa</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>q2_sequencia</t>
+          <t>Q1 - Status</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>q2_observacao</t>
+          <t>Q2 - Sequência</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>q2_status</t>
+          <t>Q2 - Observação</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>q3_resposta</t>
+          <t>Q2 - Status</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>q3_status</t>
+          <t>Q3 - Resposta</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>q4_testou_caminho</t>
+          <t>Q3 - Status</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>q4_representacao</t>
+          <t>Q4 - Testou caminho</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>q4_status</t>
+          <t>Q4 - Representação</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>q5_resposta</t>
+          <t>Q4 - Status</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>q5_status</t>
+          <t>Q5 - Resposta</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>q6_resposta</t>
+          <t>Q5 - Status</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>q6_status</t>
+          <t>Q6 - Resposta</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>q7_mudou_resposta</t>
+          <t>Q6 - Status</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>q7_justificativa</t>
+          <t>Q7 - Mudou resposta</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>q7_status</t>
+          <t>Q7 - Justificativa</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Q7 - Status</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>aluno_001.jpg</t>
+          <t>A001</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Ma Luiza Fortes</t>
+          <t>Mª Luiza Fortes</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>8°</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>8º</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>B</t>
         </is>
       </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>círculo → hexágono → triângulo invertido → estrela</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>círculo -&gt; triângulo invertido -&gt; círculo -&gt; seta -&gt; círculo</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Depois que eu li o enunciado de novo.</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>USAR o cérebro.</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>A002</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Maryana S.S</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>8º</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>(☆) → (▽) → (☆) → (৫)</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Isso era Pha ser um Pentagoho Kkkk</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>O (Pentagoho) -&gt; Pentagono (▽) -&gt; (☆) -&gt; (৫) -&gt; CHAVE</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Testei CADA círculo Até chegar em um bom camihHo</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Testando todos os outros CAMINHOS "Possíveis"</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>ver por QUAI dos círculos eu tehia que Inicia.r.</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>A003</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>ausente</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>8º</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>triângulo → estrela → lua crescente → estrela → GG → chave</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>PORQUE NÃO TICHA OUTRA</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>O COFRE.</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A004</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Nicolas</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>8º</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>diamante → seta → coração → seta → chave</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>PORQUE EU CONTEI</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>CHEGAR COM UM NUMERO MENOR</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A005</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Erick Reuer</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>8º</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Desenho de uma grade de quadrados/retângulos com setas indicando um caminho.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>balinha, coração, mais a dal deu arvore</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>revisar</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>contando para menor</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>encontrar o ciclo mais rapido</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:U6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Código</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Nome</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Nome - Status</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Ano</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Q1 - Alternativa</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Q1 - Status</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Q2 - Representação</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Q2 - Status</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Q3 - Pontos considerados</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Q3 - Somente resposta final</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Q3 - Status</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Q4 - Testou ponto</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Q4 - Explicação</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Q4 - Status</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Q5 - Resposta</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Q5 - Status</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Q6 - Resposta</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Q6 - Status</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Q7 - Mudou resposta</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Q7 - Justificativa</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Q7 - Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>A001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Maryana S.S</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>8º</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>D</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>círculo → hexágono → triângulo para baixo → estrela → chave</t>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>No mapa, o ponto '4' está marcado com um 'X'. Há setas desenhadas em várias estradas e números (1, 2, 3) escritos próximos a algumas estradas. Alguns nós (vilas) estão circulados. Os números 1, 2, 3 e 4 (opções de centro de distribuição) estão circulados. Na folha de resposta, o estudante escreveu: 'Fiz setas e marcações com os números de acordo com as estradas andadas para não me perder.'</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>com setas e marcações.</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>A parte que tive que observar com mais cuidado foi o número de estradas andadas por cada morador das vilas.</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>A002</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Laura R</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>8º</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>No mapa (IMAGEM 1), o nó 4 está circulado. Linhas são desenhadas do nó 4 para todos os outros nós no mapa. Essas linhas traçam caminhos, com alguns caminhos tendo um segmento de comprimento (por exemplo, do 4 para o 1, 2, 3, e o nó abaixo do 4) e outros tendo dois segmentos de comprimento (por exemplo, do 4 para o 1, e então para o nó acima do 1; do 4 para o 2, e então para o nó acima do 2; do 4 para o 3, e então para o nó à direita do 3). Não há texto ou outras marcações presentes no mapa.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>Tentar achar o centro que possibilite até 2 caminhos.</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>A003</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>BIANCA MACHADO</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>8º</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>No mapa, os pontos 1, 2, 3 e 4 estão circulados. O ponto 3 tem um 'X' sobre ele. Na folha de resposta, o texto '1 E 02 STO POUCO PARA FAZER UNICO QUE JOBRA E 03' está escrito.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>revisar</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>POR QUE SÃO TRÊS PONTOS PARA OS CENTROS DE DISTRIBUIÇÃO, NO</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>revisar</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>ACHAR O PONTO CERTO E MUITOS PONTOS ACABA SE PERDENDO</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A004</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>BERTHA BOEKT</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>revisar</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>8º</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>O estudante escreveu 'ANALISEI OS CAMINHOS E MARQUEI NO MAPA.'. No mapa, o estudante marcou um 'X' sobre os centros de distribuição originais (círculos verdes) nos nós 1, 2, 3, no nó à esquerda do 1 e no nó acima do 3. Há também um círculo fraco a lápis em torno do nó 4.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>revisar</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>3, 4</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>NÃO RESOLVIA PORQUE AS VILAS FICAVAM A MAIS DE DUAS ESTRADAS DO CENTRO DE DISTRIBUIÇÃO.</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>VERIFIQUEI ANALISANDO CADA CAMINHO COM SEUS NÓS.</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>revisar</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>FOI A PARTE MAIS DIFÍCIL DE DESENHAR OS CAMINHOS.</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A005</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Papilla Gomes Fracari</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>8º</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Analisei as estradas que ligam as vilas aos três centros de distribuição que já existem. Verifiquei quais vilas estariam a mais de duas estradas de distância.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Partindo de cada vila, o menor caminho até um dos centros de distribuição. Com o centro no ponto 4, todas as vilas conseguem chegar a um centro passando por no máximo duas estradas.</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>A dificuldade foi analisar todos os caminhos do mapa.</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Antes de considerar minha resposta final, conversei com meu colega e percebi que o ponto 4 era o melhor caminho.</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Código</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Nome</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atividade</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Questão</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Dados extraídos</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Arquivo questão</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Arquivo resposta</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>A003</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>As chaves do cofre</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Identificação</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>ausente</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Nome não identificado</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="K2" t="b">
-        <v>1</v>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>círculo -&gt; triângulo para baixo -&gt; círculo -&gt; seta -&gt; círculo</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>Depois que eu li o enunciado de novo.</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>USAR o cérebro.</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="R2" t="b">
-        <v>1</v>
-      </c>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>ok</t>
+          <t>A003_resposta.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>A005</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Erick Reuer</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>As chaves do cofre</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>revisar</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>testou_caminho: Não | representacao: balinha, coração, mais a dal deu arvore</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>A005_respostaa.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>A003</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>BIANCA MACHADO</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Água para Todos</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>revisar</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>representacao: No mapa, os pontos 1, 2, 3 e 4 estão circulados. O ponto 3 tem um 'X' sobre ele. Na folha de resposta, o texto '1 E 02 STO POUCO PARA FAZER UNICO QUE JOBRA E 03' está escrito.</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>A003_questao.jpg</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>A003_resposta.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A003</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>BIANCA MACHADO</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Água para Todos</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Q5</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>revisar</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>resposta: POR QUE SÃO TRÊS PONTOS PARA OS CENTROS DE DISTRIBUIÇÃO, NO</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>A003_questao.jpg</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>A003_resposta.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A004</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>BERTHA BOEKT</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Água para Todos</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Identificação</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>revisar</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>nome_estudante: BERTHA BOEKT</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>A004_questao.jpg</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>A004_resposta.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A004</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>BERTHA BOEKT</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Água para Todos</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>revisar</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>representacao: O estudante escreveu 'ANALISEI OS CAMINHOS E MARQUEI NO MAPA.'. No mapa, o estudante marcou um 'X' sobre os centros de distribuição originais (círculos verdes) nos nós 1, 2, 3, no nó à esquerda do 1 e no nó acima do 3. Há também um círculo fraco a lápis em torno do nó 4.</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>A004_questao.jpg</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>A004_resposta.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A004</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>BERTHA BOEKT</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Água para Todos</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Q5</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>revisar</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>resposta: VERIFIQUEI ANALISANDO CADA CAMINHO COM SEUS NÓS.</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>A004_questao.jpg</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>A004_resposta.jpg</t>
         </is>
       </c>
     </row>
